--- a/mock_data/data1/sensors.xlsx
+++ b/mock_data/data1/sensors.xlsx
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35.45</v>
+        <v>120.348159</v>
       </c>
       <c r="F2" t="n">
-        <v>18.77</v>
+        <v>30.321206</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67.75</v>
+        <v>120.350561</v>
       </c>
       <c r="F3" t="n">
-        <v>18.88</v>
+        <v>30.320967</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67.81</v>
+        <v>120.350716</v>
       </c>
       <c r="F4" t="n">
-        <v>54.85</v>
+        <v>30.319555</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20.58</v>
+        <v>120.348442</v>
       </c>
       <c r="F5" t="n">
-        <v>69.78</v>
+        <v>30.319592</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28.09</v>
+        <v>120.349514</v>
       </c>
       <c r="F6" t="n">
-        <v>88.59</v>
+        <v>30.320311</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.18</v>
+        <v>120.348585</v>
       </c>
       <c r="F7" t="n">
-        <v>34.54</v>
+        <v>30.321225</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>24.45</v>
+        <v>120.348908</v>
       </c>
       <c r="F8" t="n">
-        <v>34.14</v>
+        <v>30.321156</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55.22</v>
+        <v>120.350888</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>30.321027</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>56.33</v>
+        <v>120.350991</v>
       </c>
       <c r="F10" t="n">
-        <v>52.36</v>
+        <v>30.319439</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.36</v>
+        <v>120.348793</v>
       </c>
       <c r="F11" t="n">
-        <v>57.22</v>
+        <v>30.319644</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>64.89</v>
+        <v>120.349974</v>
       </c>
       <c r="F12" t="n">
-        <v>85.45999999999999</v>
+        <v>30.320333</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>54.56</v>
+        <v>120.350528</v>
       </c>
       <c r="F13" t="n">
-        <v>28.91</v>
+        <v>30.320784</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>54.19</v>
+        <v>120.35061</v>
       </c>
       <c r="F14" t="n">
-        <v>67.01000000000001</v>
+        <v>30.319174</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>33.39</v>
+        <v>120.348498</v>
       </c>
       <c r="F15" t="n">
-        <v>56.34</v>
+        <v>30.319149</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>27.45</v>
+        <v>120.349527</v>
       </c>
       <c r="F16" t="n">
-        <v>85.56</v>
+        <v>30.319955</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>26.51</v>
+        <v>120.348097</v>
       </c>
       <c r="F17" t="n">
-        <v>17.19</v>
+        <v>30.320773</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>16.07</v>
+        <v>120.348442</v>
       </c>
       <c r="F18" t="n">
-        <v>17.61</v>
+        <v>30.32079</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>33.77</v>
+        <v>120.348811</v>
       </c>
       <c r="F19" t="n">
-        <v>67.15000000000001</v>
+        <v>30.319304</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
